--- a/данные/полезно.xlsx
+++ b/данные/полезно.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\irina.mashkova\Documents\GitHub\College\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\irina.mashkova\Documents\GitHub\College\данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8889162A-FD1A-4A0F-9B73-043DC1D9FA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11107A87-C97E-43CC-A4DF-DFBAD8492D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="604" firstSheet="1" activeTab="5" xr2:uid="{626BA957-AA12-44BE-A960-46A94CAF7B15}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="604" firstSheet="2" activeTab="6" xr2:uid="{626BA957-AA12-44BE-A960-46A94CAF7B15}"/>
   </bookViews>
   <sheets>
     <sheet name="пользователи" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="расписание" sheetId="4" r:id="rId4"/>
     <sheet name="экзамены" sheetId="5" r:id="rId5"/>
     <sheet name="посещения" sheetId="6" r:id="rId6"/>
-    <sheet name="посещения (2)" sheetId="7" r:id="rId7"/>
+    <sheet name="посещения (2)" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="290">
   <si>
     <t>Ахремова</t>
   </si>
@@ -966,6 +966,15 @@
   <si>
     <t>last_name</t>
   </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>5 пара</t>
+  </si>
 </sst>
 </file>
 
@@ -1147,7 +1156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1185,11 +1194,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -36632,45 +36673,75 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B848C872-2597-451D-AAA9-AD19E1E5A1BA}">
-  <dimension ref="B2:M30"/>
+  <dimension ref="B2:AD45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.6640625" customWidth="1"/>
+    <col min="13" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="5" customWidth="1"/>
+    <col min="22" max="23" width="8.88671875" customWidth="1"/>
+    <col min="31" max="31" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:30" x14ac:dyDescent="0.3">
       <c r="C2" s="25" t="s">
         <v>277</v>
       </c>
       <c r="D2" s="25"/>
+      <c r="F2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" t="s">
+        <v>223</v>
+      </c>
       <c r="H2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="I2" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="J2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K2" t="s">
-        <v>284</v>
-      </c>
-      <c r="L2" t="s">
-        <v>285</v>
-      </c>
-      <c r="M2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M2" s="2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>7</v>
+      </c>
+      <c r="P2" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B3" s="26">
         <v>3</v>
       </c>
@@ -36680,26 +36751,61 @@
       <c r="D3" t="s">
         <v>262</v>
       </c>
-      <c r="H3">
-        <v>183</v>
+      <c r="F3">
+        <v>155</v>
+      </c>
+      <c r="G3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H3" t="s">
+        <v>278</v>
       </c>
       <c r="I3" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="J3" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="K3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N3" t="s">
+        <v>288</v>
+      </c>
+      <c r="W3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M3=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 155)</v>
+      </c>
+      <c r="X3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N3=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 155)</v>
+      </c>
+      <c r="Y3" t="str">
+        <f t="shared" ref="Y3:AA18" si="0">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O3=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 155)</v>
+      </c>
+      <c r="Z3" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 155)</v>
+      </c>
+      <c r="AA3" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 155)</v>
+      </c>
+      <c r="AB3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R3=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 155)</v>
+      </c>
+      <c r="AC3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(S3=$D$13,$D$13,$D$12)&amp;", "&amp;S$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 155)</v>
+      </c>
+      <c r="AD3" t="str">
+        <f t="shared" ref="AD3:AD30" si="1">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(T3=$D$13,$D$13,$D$12)&amp;", "&amp;T$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 155)</v>
+      </c>
+    </row>
+    <row r="4" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B4" s="26"/>
       <c r="C4">
         <v>2</v>
@@ -36707,26 +36813,58 @@
       <c r="D4" t="s">
         <v>263</v>
       </c>
-      <c r="H4">
-        <v>184</v>
+      <c r="F4">
+        <v>156</v>
+      </c>
+      <c r="G4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" t="s">
+        <v>279</v>
       </c>
       <c r="I4" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J4" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="K4" t="s">
-        <v>213</v>
-      </c>
-      <c r="L4" t="s">
-        <v>198</v>
-      </c>
-      <c r="M4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="W4" t="str">
+        <f t="shared" ref="W4:X30" si="2">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M4=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 156)</v>
+      </c>
+      <c r="X4" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 156)</v>
+      </c>
+      <c r="Y4" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 156)</v>
+      </c>
+      <c r="Z4" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 156)</v>
+      </c>
+      <c r="AA4" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 156)</v>
+      </c>
+      <c r="AB4" t="str">
+        <f t="shared" ref="AB4:AB30" si="3">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R4=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 156)</v>
+      </c>
+      <c r="AC4" t="str">
+        <f t="shared" ref="AC4:AC30" si="4">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(S4=$D$13,$D$13,$D$12)&amp;", "&amp;S$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 156)</v>
+      </c>
+      <c r="AD4" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 156)</v>
+      </c>
+    </row>
+    <row r="5" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B5" s="26"/>
       <c r="C5">
         <v>7</v>
@@ -36734,26 +36872,58 @@
       <c r="D5" t="s">
         <v>264</v>
       </c>
-      <c r="H5">
-        <v>185</v>
+      <c r="F5">
+        <v>157</v>
+      </c>
+      <c r="G5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" t="s">
+        <v>280</v>
       </c>
       <c r="I5" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J5" t="s">
-        <v>280</v>
+        <v>197</v>
       </c>
       <c r="K5" t="s">
-        <v>213</v>
-      </c>
-      <c r="L5" t="s">
-        <v>197</v>
-      </c>
-      <c r="M5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="W5" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 157)</v>
+      </c>
+      <c r="X5" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 157)</v>
+      </c>
+      <c r="Y5" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 157)</v>
+      </c>
+      <c r="Z5" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 157)</v>
+      </c>
+      <c r="AA5" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 157)</v>
+      </c>
+      <c r="AB5" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 157)</v>
+      </c>
+      <c r="AC5" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 157)</v>
+      </c>
+      <c r="AD5" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 157)</v>
+      </c>
+    </row>
+    <row r="6" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B6" s="26"/>
       <c r="C6">
         <v>9</v>
@@ -36761,26 +36931,67 @@
       <c r="D6" t="s">
         <v>265</v>
       </c>
-      <c r="H6">
-        <v>186</v>
+      <c r="F6">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" t="s">
+        <v>278</v>
       </c>
       <c r="I6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J6" t="s">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="K6" t="s">
-        <v>214</v>
-      </c>
-      <c r="L6" t="s">
-        <v>199</v>
-      </c>
-      <c r="M6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N6" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>288</v>
+      </c>
+      <c r="T6" t="s">
+        <v>288</v>
+      </c>
+      <c r="W6" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 158)</v>
+      </c>
+      <c r="X6" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 158)</v>
+      </c>
+      <c r="Y6" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 158)</v>
+      </c>
+      <c r="Z6" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 158)</v>
+      </c>
+      <c r="AA6" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 14, 158)</v>
+      </c>
+      <c r="AB6" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 158)</v>
+      </c>
+      <c r="AC6" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 158)</v>
+      </c>
+      <c r="AD6" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 158)</v>
+      </c>
+    </row>
+    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B7" s="26"/>
       <c r="C7">
         <v>14</v>
@@ -36788,26 +36999,64 @@
       <c r="D7" t="s">
         <v>266</v>
       </c>
-      <c r="H7">
-        <v>187</v>
+      <c r="F7">
+        <v>159</v>
+      </c>
+      <c r="G7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H7" t="s">
+        <v>279</v>
       </c>
       <c r="I7" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J7" t="s">
-        <v>279</v>
+        <v>203</v>
       </c>
       <c r="K7" t="s">
-        <v>214</v>
-      </c>
-      <c r="L7" t="s">
-        <v>203</v>
-      </c>
-      <c r="M7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N7" t="s">
+        <v>288</v>
+      </c>
+      <c r="T7" t="s">
+        <v>288</v>
+      </c>
+      <c r="W7" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 159)</v>
+      </c>
+      <c r="X7" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 159)</v>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 159)</v>
+      </c>
+      <c r="Z7" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 159)</v>
+      </c>
+      <c r="AA7" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 159)</v>
+      </c>
+      <c r="AB7" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 159)</v>
+      </c>
+      <c r="AC7" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 159)</v>
+      </c>
+      <c r="AD7" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 159)</v>
+      </c>
+    </row>
+    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B8" s="26"/>
       <c r="C8">
         <v>15</v>
@@ -36815,26 +37064,64 @@
       <c r="D8" t="s">
         <v>267</v>
       </c>
-      <c r="H8">
-        <v>188</v>
+      <c r="F8">
+        <v>160</v>
+      </c>
+      <c r="G8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H8" t="s">
+        <v>280</v>
       </c>
       <c r="I8" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J8" t="s">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="K8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" t="s">
-        <v>132</v>
-      </c>
-      <c r="M8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N8" t="s">
+        <v>288</v>
+      </c>
+      <c r="T8" t="s">
+        <v>288</v>
+      </c>
+      <c r="W8" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 160)</v>
+      </c>
+      <c r="X8" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 160)</v>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 160)</v>
+      </c>
+      <c r="Z8" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 160)</v>
+      </c>
+      <c r="AA8" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 160)</v>
+      </c>
+      <c r="AB8" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 160)</v>
+      </c>
+      <c r="AC8" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 160)</v>
+      </c>
+      <c r="AD8" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 160)</v>
+      </c>
+    </row>
+    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B9" s="26"/>
       <c r="C9">
         <v>18</v>
@@ -36842,26 +37129,61 @@
       <c r="D9" t="s">
         <v>268</v>
       </c>
-      <c r="H9">
-        <v>189</v>
+      <c r="F9">
+        <v>161</v>
+      </c>
+      <c r="G9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" t="s">
+        <v>278</v>
       </c>
       <c r="I9" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="J9" t="s">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="K9" t="s">
-        <v>213</v>
-      </c>
-      <c r="L9" t="s">
-        <v>199</v>
-      </c>
-      <c r="M9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="Q9" t="s">
+        <v>288</v>
+      </c>
+      <c r="W9" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 161)</v>
+      </c>
+      <c r="X9" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 161)</v>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 161)</v>
+      </c>
+      <c r="Z9" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 161)</v>
+      </c>
+      <c r="AA9" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 14, 161)</v>
+      </c>
+      <c r="AB9" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 161)</v>
+      </c>
+      <c r="AC9" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 161)</v>
+      </c>
+      <c r="AD9" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 161)</v>
+      </c>
+    </row>
+    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B10" s="26"/>
       <c r="C10">
         <v>23</v>
@@ -36869,426 +37191,1829 @@
       <c r="D10" t="s">
         <v>269</v>
       </c>
-      <c r="H10">
-        <v>190</v>
+      <c r="F10">
+        <v>162</v>
+      </c>
+      <c r="G10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H10" t="s">
+        <v>279</v>
       </c>
       <c r="I10" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="J10" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>213</v>
-      </c>
-      <c r="L10" t="s">
-        <v>198</v>
-      </c>
-      <c r="M10" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="W10" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 162)</v>
+      </c>
+      <c r="X10" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 162)</v>
+      </c>
+      <c r="Y10" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 162)</v>
+      </c>
+      <c r="Z10" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 162)</v>
+      </c>
+      <c r="AA10" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 162)</v>
+      </c>
+      <c r="AB10" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 162)</v>
+      </c>
+      <c r="AC10" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 162)</v>
+      </c>
+      <c r="AD10" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 162)</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>270</v>
       </c>
-      <c r="H11">
-        <v>191</v>
+      <c r="F11">
+        <v>163</v>
+      </c>
+      <c r="G11" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" t="s">
+        <v>281</v>
       </c>
       <c r="I11" t="s">
+        <v>213</v>
+      </c>
+      <c r="J11" t="s">
+        <v>205</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="N11" t="s">
+        <v>288</v>
+      </c>
+      <c r="W11" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 163)</v>
+      </c>
+      <c r="X11" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 163)</v>
+      </c>
+      <c r="Y11" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 163)</v>
+      </c>
+      <c r="Z11" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 163)</v>
+      </c>
+      <c r="AA11" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 163)</v>
+      </c>
+      <c r="AB11" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 163)</v>
+      </c>
+      <c r="AC11" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 163)</v>
+      </c>
+      <c r="AD11" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 163)</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12">
+        <v>164</v>
+      </c>
+      <c r="G12" t="s">
+        <v>231</v>
+      </c>
+      <c r="H12" t="s">
+        <v>278</v>
+      </c>
+      <c r="I12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" t="s">
+        <v>197</v>
+      </c>
+      <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" t="s">
+        <v>288</v>
+      </c>
+      <c r="T12" t="s">
+        <v>288</v>
+      </c>
+      <c r="W12" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 164)</v>
+      </c>
+      <c r="X12" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 164)</v>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 164)</v>
+      </c>
+      <c r="Z12" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 164)</v>
+      </c>
+      <c r="AA12" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 164)</v>
+      </c>
+      <c r="AB12" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 164)</v>
+      </c>
+      <c r="AC12" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 164)</v>
+      </c>
+      <c r="AD12" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 164)</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13">
+        <v>165</v>
+      </c>
+      <c r="G13" t="s">
+        <v>231</v>
+      </c>
+      <c r="H13" t="s">
+        <v>279</v>
+      </c>
+      <c r="I13" t="s">
+        <v>215</v>
+      </c>
+      <c r="J13" t="s">
+        <v>203</v>
+      </c>
+      <c r="K13" t="s">
+        <v>82</v>
+      </c>
+      <c r="W13" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 165)</v>
+      </c>
+      <c r="X13" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 165)</v>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 165)</v>
+      </c>
+      <c r="Z13" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 165)</v>
+      </c>
+      <c r="AA13" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 165)</v>
+      </c>
+      <c r="AB13" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 165)</v>
+      </c>
+      <c r="AC13" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 165)</v>
+      </c>
+      <c r="AD13" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 165)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>166</v>
+      </c>
+      <c r="G14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" t="s">
+        <v>281</v>
+      </c>
+      <c r="I14" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" t="s">
+        <v>203</v>
+      </c>
+      <c r="K14" t="s">
+        <v>82</v>
+      </c>
+      <c r="W14" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 166)</v>
+      </c>
+      <c r="X14" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 166)</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 166)</v>
+      </c>
+      <c r="Z14" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 166)</v>
+      </c>
+      <c r="AA14" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 166)</v>
+      </c>
+      <c r="AB14" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 166)</v>
+      </c>
+      <c r="AC14" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 166)</v>
+      </c>
+      <c r="AD14" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 166)</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>167</v>
+      </c>
+      <c r="G15" t="s">
+        <v>232</v>
+      </c>
+      <c r="H15" t="s">
+        <v>278</v>
+      </c>
+      <c r="I15" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" t="s">
+        <v>132</v>
+      </c>
+      <c r="K15" t="s">
+        <v>93</v>
+      </c>
+      <c r="W15" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 167)</v>
+      </c>
+      <c r="X15" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 167)</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 167)</v>
+      </c>
+      <c r="Z15" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 167)</v>
+      </c>
+      <c r="AA15" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 167)</v>
+      </c>
+      <c r="AB15" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 167)</v>
+      </c>
+      <c r="AC15" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 167)</v>
+      </c>
+      <c r="AD15" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 167)</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>168</v>
+      </c>
+      <c r="G16" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" t="s">
+        <v>279</v>
+      </c>
+      <c r="I16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J16" t="s">
+        <v>205</v>
+      </c>
+      <c r="K16" t="s">
+        <v>92</v>
+      </c>
+      <c r="N16" t="s">
+        <v>288</v>
+      </c>
+      <c r="W16" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 168)</v>
+      </c>
+      <c r="X16" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 168)</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 168)</v>
+      </c>
+      <c r="Z16" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 168)</v>
+      </c>
+      <c r="AA16" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 168)</v>
+      </c>
+      <c r="AB16" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 168)</v>
+      </c>
+      <c r="AC16" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 168)</v>
+      </c>
+      <c r="AD16" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 168)</v>
+      </c>
+    </row>
+    <row r="17" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>169</v>
+      </c>
+      <c r="G17" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" t="s">
+        <v>278</v>
+      </c>
+      <c r="I17" t="s">
+        <v>214</v>
+      </c>
+      <c r="J17" t="s">
+        <v>198</v>
+      </c>
+      <c r="K17" t="s">
+        <v>73</v>
+      </c>
+      <c r="N17" t="s">
+        <v>288</v>
+      </c>
+      <c r="W17" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 169)</v>
+      </c>
+      <c r="X17" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 169)</v>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 169)</v>
+      </c>
+      <c r="Z17" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 169)</v>
+      </c>
+      <c r="AA17" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 169)</v>
+      </c>
+      <c r="AB17" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 169)</v>
+      </c>
+      <c r="AC17" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 169)</v>
+      </c>
+      <c r="AD17" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 169)</v>
+      </c>
+    </row>
+    <row r="18" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>170</v>
+      </c>
+      <c r="G18" t="s">
+        <v>228</v>
+      </c>
+      <c r="H18" t="s">
+        <v>279</v>
+      </c>
+      <c r="I18" t="s">
+        <v>213</v>
+      </c>
+      <c r="J18" t="s">
+        <v>198</v>
+      </c>
+      <c r="K18" t="s">
+        <v>73</v>
+      </c>
+      <c r="W18" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 170)</v>
+      </c>
+      <c r="X18" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 170)</v>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 170)</v>
+      </c>
+      <c r="Z18" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 170)</v>
+      </c>
+      <c r="AA18" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 170)</v>
+      </c>
+      <c r="AB18" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 170)</v>
+      </c>
+      <c r="AC18" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 170)</v>
+      </c>
+      <c r="AD18" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 170)</v>
+      </c>
+    </row>
+    <row r="19" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>171</v>
+      </c>
+      <c r="G19" t="s">
+        <v>228</v>
+      </c>
+      <c r="H19" t="s">
+        <v>280</v>
+      </c>
+      <c r="I19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" t="s">
+        <v>197</v>
+      </c>
+      <c r="K19" t="s">
+        <v>88</v>
+      </c>
+      <c r="W19" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 171)</v>
+      </c>
+      <c r="X19" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 171)</v>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" ref="Y19:Y30" si="5">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O19=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F19&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 171)</v>
+      </c>
+      <c r="Z19" t="str">
+        <f t="shared" ref="Z19:Z30" si="6">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P19=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F19&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 171)</v>
+      </c>
+      <c r="AA19" t="str">
+        <f t="shared" ref="AA19:AA30" si="7">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q19=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F19&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 171)</v>
+      </c>
+      <c r="AB19" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 171)</v>
+      </c>
+      <c r="AC19" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 171)</v>
+      </c>
+      <c r="AD19" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 171)</v>
+      </c>
+    </row>
+    <row r="20" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>172</v>
+      </c>
+      <c r="G20" t="s">
+        <v>229</v>
+      </c>
+      <c r="H20" t="s">
+        <v>278</v>
+      </c>
+      <c r="I20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" t="s">
+        <v>199</v>
+      </c>
+      <c r="K20" t="s">
+        <v>78</v>
+      </c>
+      <c r="N20" t="s">
+        <v>288</v>
+      </c>
+      <c r="T20" t="s">
+        <v>288</v>
+      </c>
+      <c r="W20" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 172)</v>
+      </c>
+      <c r="X20" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 172)</v>
+      </c>
+      <c r="Y20" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 172)</v>
+      </c>
+      <c r="Z20" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 172)</v>
+      </c>
+      <c r="AA20" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 172)</v>
+      </c>
+      <c r="AB20" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 172)</v>
+      </c>
+      <c r="AC20" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 172)</v>
+      </c>
+      <c r="AD20" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 172)</v>
+      </c>
+    </row>
+    <row r="21" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>173</v>
+      </c>
+      <c r="G21" t="s">
+        <v>229</v>
+      </c>
+      <c r="H21" t="s">
+        <v>279</v>
+      </c>
+      <c r="I21" t="s">
+        <v>214</v>
+      </c>
+      <c r="J21" t="s">
+        <v>203</v>
+      </c>
+      <c r="K21" t="s">
+        <v>82</v>
+      </c>
+      <c r="N21" t="s">
+        <v>288</v>
+      </c>
+      <c r="T21" t="s">
+        <v>288</v>
+      </c>
+      <c r="W21" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 173)</v>
+      </c>
+      <c r="X21" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 173)</v>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 173)</v>
+      </c>
+      <c r="Z21" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 173)</v>
+      </c>
+      <c r="AA21" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 173)</v>
+      </c>
+      <c r="AB21" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 173)</v>
+      </c>
+      <c r="AC21" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 173)</v>
+      </c>
+      <c r="AD21" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 173)</v>
+      </c>
+    </row>
+    <row r="22" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>174</v>
+      </c>
+      <c r="G22" t="s">
+        <v>229</v>
+      </c>
+      <c r="H22" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" t="s">
+        <v>214</v>
+      </c>
+      <c r="J22" t="s">
+        <v>132</v>
+      </c>
+      <c r="K22" t="s">
+        <v>93</v>
+      </c>
+      <c r="N22" t="s">
+        <v>288</v>
+      </c>
+      <c r="T22" t="s">
+        <v>288</v>
+      </c>
+      <c r="W22" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 174)</v>
+      </c>
+      <c r="X22" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 174)</v>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 174)</v>
+      </c>
+      <c r="Z22" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 174)</v>
+      </c>
+      <c r="AA22" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 174)</v>
+      </c>
+      <c r="AB22" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 174)</v>
+      </c>
+      <c r="AC22" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 174)</v>
+      </c>
+      <c r="AD22" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 174)</v>
+      </c>
+    </row>
+    <row r="23" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>175</v>
+      </c>
+      <c r="G23" t="s">
         <v>230</v>
       </c>
-      <c r="J11" t="s">
+      <c r="H23" t="s">
+        <v>278</v>
+      </c>
+      <c r="I23" t="s">
+        <v>213</v>
+      </c>
+      <c r="J23" t="s">
+        <v>199</v>
+      </c>
+      <c r="K23" t="s">
+        <v>78</v>
+      </c>
+      <c r="M23" t="s">
+        <v>288</v>
+      </c>
+      <c r="W23" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 175)</v>
+      </c>
+      <c r="X23" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 175)</v>
+      </c>
+      <c r="Y23" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 175)</v>
+      </c>
+      <c r="Z23" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 175)</v>
+      </c>
+      <c r="AA23" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 175)</v>
+      </c>
+      <c r="AB23" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 175)</v>
+      </c>
+      <c r="AC23" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 175)</v>
+      </c>
+      <c r="AD23" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 175)</v>
+      </c>
+    </row>
+    <row r="24" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>176</v>
+      </c>
+      <c r="G24" t="s">
+        <v>230</v>
+      </c>
+      <c r="H24" t="s">
+        <v>279</v>
+      </c>
+      <c r="I24" t="s">
+        <v>213</v>
+      </c>
+      <c r="J24" t="s">
+        <v>198</v>
+      </c>
+      <c r="K24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M24" t="s">
+        <v>288</v>
+      </c>
+      <c r="W24" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 176)</v>
+      </c>
+      <c r="X24" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 176)</v>
+      </c>
+      <c r="Y24" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 176)</v>
+      </c>
+      <c r="Z24" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 176)</v>
+      </c>
+      <c r="AA24" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 176)</v>
+      </c>
+      <c r="AB24" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 176)</v>
+      </c>
+      <c r="AC24" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 176)</v>
+      </c>
+      <c r="AD24" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 176)</v>
+      </c>
+    </row>
+    <row r="25" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>177</v>
+      </c>
+      <c r="G25" t="s">
+        <v>230</v>
+      </c>
+      <c r="H25" t="s">
         <v>281</v>
       </c>
-      <c r="K11" t="s">
+      <c r="I25" t="s">
         <v>213</v>
       </c>
-      <c r="L11" t="s">
+      <c r="J25" t="s">
         <v>205</v>
       </c>
-      <c r="M11" t="s">
+      <c r="K25" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H12">
-        <v>192</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="M25" t="s">
+        <v>288</v>
+      </c>
+      <c r="N25" t="s">
+        <v>288</v>
+      </c>
+      <c r="W25" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 177)</v>
+      </c>
+      <c r="X25" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 177)</v>
+      </c>
+      <c r="Y25" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 177)</v>
+      </c>
+      <c r="Z25" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 177)</v>
+      </c>
+      <c r="AA25" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 177)</v>
+      </c>
+      <c r="AB25" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 177)</v>
+      </c>
+      <c r="AC25" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 177)</v>
+      </c>
+      <c r="AD25" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 177)</v>
+      </c>
+    </row>
+    <row r="26" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>178</v>
+      </c>
+      <c r="G26" t="s">
         <v>231</v>
       </c>
-      <c r="J12" t="s">
+      <c r="H26" t="s">
         <v>278</v>
       </c>
-      <c r="K12" t="s">
+      <c r="I26" t="s">
         <v>214</v>
       </c>
-      <c r="L12" t="s">
+      <c r="J26" t="s">
         <v>197</v>
       </c>
-      <c r="M12" t="s">
+      <c r="K26" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <v>193</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="M26" t="s">
+        <v>288</v>
+      </c>
+      <c r="N26" t="s">
+        <v>288</v>
+      </c>
+      <c r="T26" t="s">
+        <v>288</v>
+      </c>
+      <c r="W26" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 178)</v>
+      </c>
+      <c r="X26" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 178)</v>
+      </c>
+      <c r="Y26" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 178)</v>
+      </c>
+      <c r="Z26" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 178)</v>
+      </c>
+      <c r="AA26" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 178)</v>
+      </c>
+      <c r="AB26" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 178)</v>
+      </c>
+      <c r="AC26" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 178)</v>
+      </c>
+      <c r="AD26" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 23, 178)</v>
+      </c>
+    </row>
+    <row r="27" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>179</v>
+      </c>
+      <c r="G27" t="s">
         <v>231</v>
       </c>
-      <c r="J13" t="s">
+      <c r="H27" t="s">
         <v>279</v>
       </c>
-      <c r="K13" t="s">
-        <v>215</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="I27" t="s">
+        <v>213</v>
+      </c>
+      <c r="J27" t="s">
         <v>203</v>
       </c>
-      <c r="M13" t="s">
+      <c r="K27" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H14">
-        <v>194</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="M27" t="s">
+        <v>288</v>
+      </c>
+      <c r="W27" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 179)</v>
+      </c>
+      <c r="X27" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 179)</v>
+      </c>
+      <c r="Y27" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 179)</v>
+      </c>
+      <c r="Z27" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 179)</v>
+      </c>
+      <c r="AA27" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 179)</v>
+      </c>
+      <c r="AB27" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 179)</v>
+      </c>
+      <c r="AC27" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 179)</v>
+      </c>
+      <c r="AD27" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 179)</v>
+      </c>
+    </row>
+    <row r="28" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>180</v>
+      </c>
+      <c r="G28" t="s">
         <v>231</v>
       </c>
-      <c r="J14" t="s">
+      <c r="H28" t="s">
         <v>281</v>
       </c>
-      <c r="K14" t="s">
-        <v>215</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="I28" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" t="s">
         <v>203</v>
       </c>
-      <c r="M14" t="s">
+      <c r="K28" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H15">
-        <v>195</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="M28" t="s">
+        <v>288</v>
+      </c>
+      <c r="W28" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 180)</v>
+      </c>
+      <c r="X28" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 180)</v>
+      </c>
+      <c r="Y28" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 180)</v>
+      </c>
+      <c r="Z28" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 180)</v>
+      </c>
+      <c r="AA28" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 180)</v>
+      </c>
+      <c r="AB28" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 180)</v>
+      </c>
+      <c r="AC28" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 180)</v>
+      </c>
+      <c r="AD28" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 180)</v>
+      </c>
+    </row>
+    <row r="29" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>181</v>
+      </c>
+      <c r="G29" t="s">
         <v>232</v>
       </c>
-      <c r="J15" t="s">
+      <c r="H29" t="s">
         <v>278</v>
       </c>
-      <c r="K15" t="s">
-        <v>215</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="I29" t="s">
+        <v>213</v>
+      </c>
+      <c r="J29" t="s">
         <v>132</v>
       </c>
-      <c r="M15" t="s">
+      <c r="K29" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H16">
-        <v>196</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="M29" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>288</v>
+      </c>
+      <c r="W29" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 181)</v>
+      </c>
+      <c r="X29" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 181)</v>
+      </c>
+      <c r="Y29" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 181)</v>
+      </c>
+      <c r="Z29" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 181)</v>
+      </c>
+      <c r="AA29" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 14, 181)</v>
+      </c>
+      <c r="AB29" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 181)</v>
+      </c>
+      <c r="AC29" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 181)</v>
+      </c>
+      <c r="AD29" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 181)</v>
+      </c>
+    </row>
+    <row r="30" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>182</v>
+      </c>
+      <c r="G30" t="s">
         <v>232</v>
       </c>
-      <c r="J16" t="s">
+      <c r="H30" t="s">
         <v>279</v>
       </c>
-      <c r="K16" t="s">
+      <c r="I30" t="s">
         <v>213</v>
       </c>
-      <c r="L16" t="s">
+      <c r="J30" t="s">
         <v>205</v>
       </c>
-      <c r="M16" t="s">
+      <c r="K30" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H17">
+      <c r="M30" t="s">
+        <v>288</v>
+      </c>
+      <c r="N30" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>288</v>
+      </c>
+      <c r="W30" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 1, 182)</v>
+      </c>
+      <c r="X30" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 2, 182)</v>
+      </c>
+      <c r="Y30" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 182)</v>
+      </c>
+      <c r="Z30" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 182)</v>
+      </c>
+      <c r="AA30" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 14, 182)</v>
+      </c>
+      <c r="AB30" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 182)</v>
+      </c>
+      <c r="AC30" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 182)</v>
+      </c>
+      <c r="AD30" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 182)</v>
+      </c>
+    </row>
+    <row r="33" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="M33" s="2">
+        <v>1</v>
+      </c>
+      <c r="N33" s="2">
+        <v>2</v>
+      </c>
+      <c r="O33" s="2">
+        <v>7</v>
+      </c>
+      <c r="P33" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>14</v>
+      </c>
+      <c r="R33" s="2">
+        <v>15</v>
+      </c>
+      <c r="S33" s="2">
+        <v>18</v>
+      </c>
+      <c r="T33" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F34">
+        <v>471</v>
+      </c>
+      <c r="G34" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" t="s">
+        <v>281</v>
+      </c>
+      <c r="I34" t="s">
+        <v>239</v>
+      </c>
+      <c r="J34" t="s">
         <v>197</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K34" t="s">
+        <v>88</v>
+      </c>
+      <c r="W34" t="str">
+        <f t="shared" ref="W31:W42" si="8">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M34=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 471)</v>
+      </c>
+      <c r="X34" t="str">
+        <f t="shared" ref="X31:X42" si="9">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N34=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 471)</v>
+      </c>
+      <c r="Y34" t="str">
+        <f t="shared" ref="Y31:Y42" si="10">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O34=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 471)</v>
+      </c>
+      <c r="Z34" t="str">
+        <f t="shared" ref="Z31:Z42" si="11">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P34=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 471)</v>
+      </c>
+      <c r="AA34" t="str">
+        <f t="shared" ref="AA31:AA42" si="12">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q34=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 471)</v>
+      </c>
+      <c r="AB34" t="str">
+        <f t="shared" ref="AB31:AB42" si="13">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R34=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 471)</v>
+      </c>
+      <c r="AC34" t="str">
+        <f t="shared" ref="AC31:AC42" si="14">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(S34=$D$13,$D$13,$D$12)&amp;", "&amp;S$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 471)</v>
+      </c>
+      <c r="AD34" t="str">
+        <f t="shared" ref="AD31:AD42" si="15">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(T34=$D$13,$D$13,$D$12)&amp;", "&amp;T$2&amp;", "&amp;$F34&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 471)</v>
+      </c>
+    </row>
+    <row r="35" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <v>459</v>
+      </c>
+      <c r="G35" t="s">
+        <v>229</v>
+      </c>
+      <c r="H35" t="s">
+        <v>279</v>
+      </c>
+      <c r="I35" t="s">
+        <v>239</v>
+      </c>
+      <c r="J35" t="s">
+        <v>197</v>
+      </c>
+      <c r="K35" t="s">
+        <v>88</v>
+      </c>
+      <c r="W35" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 459)</v>
+      </c>
+      <c r="X35" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 459)</v>
+      </c>
+      <c r="Y35" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 459)</v>
+      </c>
+      <c r="Z35" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 459)</v>
+      </c>
+      <c r="AA35" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 459)</v>
+      </c>
+      <c r="AB35" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 459)</v>
+      </c>
+      <c r="AC35" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 459)</v>
+      </c>
+      <c r="AD35" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 459)</v>
+      </c>
+    </row>
+    <row r="36" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <v>461</v>
+      </c>
+      <c r="G36" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" t="s">
+        <v>282</v>
+      </c>
+      <c r="I36" t="s">
+        <v>239</v>
+      </c>
+      <c r="J36" t="s">
+        <v>205</v>
+      </c>
+      <c r="K36" t="s">
+        <v>92</v>
+      </c>
+      <c r="W36" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 461)</v>
+      </c>
+      <c r="X36" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 461)</v>
+      </c>
+      <c r="Y36" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 461)</v>
+      </c>
+      <c r="Z36" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 461)</v>
+      </c>
+      <c r="AA36" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 461)</v>
+      </c>
+      <c r="AB36" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 461)</v>
+      </c>
+      <c r="AC36" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 461)</v>
+      </c>
+      <c r="AD36" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 461)</v>
+      </c>
+    </row>
+    <row r="37" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <v>473</v>
+      </c>
+      <c r="G37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I37" t="s">
+        <v>239</v>
+      </c>
+      <c r="J37" t="s">
+        <v>205</v>
+      </c>
+      <c r="K37" t="s">
+        <v>92</v>
+      </c>
+      <c r="W37" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 473)</v>
+      </c>
+      <c r="X37" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 473)</v>
+      </c>
+      <c r="Y37" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 473)</v>
+      </c>
+      <c r="Z37" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 473)</v>
+      </c>
+      <c r="AA37" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 473)</v>
+      </c>
+      <c r="AB37" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 473)</v>
+      </c>
+      <c r="AC37" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 473)</v>
+      </c>
+      <c r="AD37" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 473)</v>
+      </c>
+    </row>
+    <row r="38" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <v>462</v>
+      </c>
+      <c r="G38" t="s">
+        <v>231</v>
+      </c>
+      <c r="H38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I38" t="s">
+        <v>239</v>
+      </c>
+      <c r="J38" t="s">
+        <v>199</v>
+      </c>
+      <c r="K38" t="s">
+        <v>78</v>
+      </c>
+      <c r="W38" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 462)</v>
+      </c>
+      <c r="X38" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 462)</v>
+      </c>
+      <c r="Y38" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 462)</v>
+      </c>
+      <c r="Z38" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 462)</v>
+      </c>
+      <c r="AA38" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 462)</v>
+      </c>
+      <c r="AB38" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 462)</v>
+      </c>
+      <c r="AC38" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 462)</v>
+      </c>
+      <c r="AD38" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 462)</v>
+      </c>
+    </row>
+    <row r="39" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <v>474</v>
+      </c>
+      <c r="G39" t="s">
+        <v>231</v>
+      </c>
+      <c r="H39" t="s">
+        <v>281</v>
+      </c>
+      <c r="I39" t="s">
+        <v>239</v>
+      </c>
+      <c r="J39" t="s">
+        <v>199</v>
+      </c>
+      <c r="K39" t="s">
+        <v>78</v>
+      </c>
+      <c r="W39" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 474)</v>
+      </c>
+      <c r="X39" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 474)</v>
+      </c>
+      <c r="Y39" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 474)</v>
+      </c>
+      <c r="Z39" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 474)</v>
+      </c>
+      <c r="AA39" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 474)</v>
+      </c>
+      <c r="AB39" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 474)</v>
+      </c>
+      <c r="AC39" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 474)</v>
+      </c>
+      <c r="AD39" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 474)</v>
+      </c>
+    </row>
+    <row r="40" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <v>470</v>
+      </c>
+      <c r="G40" t="s">
         <v>228</v>
       </c>
-      <c r="J17" t="s">
-        <v>278</v>
-      </c>
-      <c r="K17" t="s">
-        <v>214</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="H40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I40" t="s">
+        <v>240</v>
+      </c>
+      <c r="J40" t="s">
+        <v>132</v>
+      </c>
+      <c r="K40" t="s">
+        <v>93</v>
+      </c>
+      <c r="W40" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 470)</v>
+      </c>
+      <c r="X40" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 470)</v>
+      </c>
+      <c r="Y40" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 470)</v>
+      </c>
+      <c r="Z40" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 470)</v>
+      </c>
+      <c r="AA40" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 470)</v>
+      </c>
+      <c r="AB40" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 470)</v>
+      </c>
+      <c r="AC40" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 470)</v>
+      </c>
+      <c r="AD40" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 470)</v>
+      </c>
+    </row>
+    <row r="41" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <v>458</v>
+      </c>
+      <c r="G41" t="s">
+        <v>228</v>
+      </c>
+      <c r="H41" t="s">
+        <v>279</v>
+      </c>
+      <c r="I41" t="s">
+        <v>240</v>
+      </c>
+      <c r="J41" t="s">
+        <v>132</v>
+      </c>
+      <c r="K41" t="s">
+        <v>93</v>
+      </c>
+      <c r="W41" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 458)</v>
+      </c>
+      <c r="X41" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 458)</v>
+      </c>
+      <c r="Y41" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 458)</v>
+      </c>
+      <c r="Z41" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 458)</v>
+      </c>
+      <c r="AA41" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 458)</v>
+      </c>
+      <c r="AB41" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 458)</v>
+      </c>
+      <c r="AC41" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 458)</v>
+      </c>
+      <c r="AD41" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 458)</v>
+      </c>
+    </row>
+    <row r="42" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <v>457</v>
+      </c>
+      <c r="G42" t="s">
+        <v>230</v>
+      </c>
+      <c r="H42" t="s">
+        <v>279</v>
+      </c>
+      <c r="I42" t="s">
+        <v>240</v>
+      </c>
+      <c r="J42" t="s">
+        <v>203</v>
+      </c>
+      <c r="K42" t="s">
+        <v>82</v>
+      </c>
+      <c r="W42" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 457)</v>
+      </c>
+      <c r="X42" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 457)</v>
+      </c>
+      <c r="Y42" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 457)</v>
+      </c>
+      <c r="Z42" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 457)</v>
+      </c>
+      <c r="AA42" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 457)</v>
+      </c>
+      <c r="AB42" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 457)</v>
+      </c>
+      <c r="AC42" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 457)</v>
+      </c>
+      <c r="AD42" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 457)</v>
+      </c>
+    </row>
+    <row r="43" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <v>469</v>
+      </c>
+      <c r="G43" t="s">
+        <v>230</v>
+      </c>
+      <c r="H43" t="s">
+        <v>281</v>
+      </c>
+      <c r="I43" t="s">
+        <v>240</v>
+      </c>
+      <c r="J43" t="s">
+        <v>203</v>
+      </c>
+      <c r="K43" t="s">
+        <v>82</v>
+      </c>
+      <c r="W43" t="str">
+        <f t="shared" ref="W43:W45" si="16">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M43=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 469)</v>
+      </c>
+      <c r="X43" t="str">
+        <f t="shared" ref="X43:X45" si="17">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N43=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 469)</v>
+      </c>
+      <c r="Y43" t="str">
+        <f t="shared" ref="Y43:Y45" si="18">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O43=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 469)</v>
+      </c>
+      <c r="Z43" t="str">
+        <f t="shared" ref="Z43:Z45" si="19">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P43=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 469)</v>
+      </c>
+      <c r="AA43" t="str">
+        <f t="shared" ref="AA43:AA45" si="20">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q43=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 469)</v>
+      </c>
+      <c r="AB43" t="str">
+        <f t="shared" ref="AB43:AB45" si="21">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R43=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 469)</v>
+      </c>
+      <c r="AC43" t="str">
+        <f t="shared" ref="AC43:AC45" si="22">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(S43=$D$13,$D$13,$D$12)&amp;", "&amp;S$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 469)</v>
+      </c>
+      <c r="AD43" t="str">
+        <f t="shared" ref="AD43:AD45" si="23">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(T43=$D$13,$D$13,$D$12)&amp;", "&amp;T$2&amp;", "&amp;$F43&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 469)</v>
+      </c>
+    </row>
+    <row r="44" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <v>460</v>
+      </c>
+      <c r="G44" t="s">
+        <v>232</v>
+      </c>
+      <c r="H44" t="s">
+        <v>279</v>
+      </c>
+      <c r="I44" t="s">
+        <v>240</v>
+      </c>
+      <c r="J44" t="s">
         <v>198</v>
       </c>
-      <c r="M17" t="s">
+      <c r="K44" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H18">
+      <c r="W44" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 460)</v>
+      </c>
+      <c r="X44" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 460)</v>
+      </c>
+      <c r="Y44" t="str">
+        <f t="shared" si="18"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 460)</v>
+      </c>
+      <c r="Z44" t="str">
+        <f t="shared" si="19"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 460)</v>
+      </c>
+      <c r="AA44" t="str">
+        <f t="shared" si="20"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 460)</v>
+      </c>
+      <c r="AB44" t="str">
+        <f t="shared" si="21"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 460)</v>
+      </c>
+      <c r="AC44" t="str">
+        <f t="shared" si="22"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 460)</v>
+      </c>
+      <c r="AD44" t="str">
+        <f t="shared" si="23"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 460)</v>
+      </c>
+    </row>
+    <row r="45" spans="6:30" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <v>472</v>
+      </c>
+      <c r="G45" t="s">
+        <v>232</v>
+      </c>
+      <c r="H45" t="s">
+        <v>281</v>
+      </c>
+      <c r="I45" t="s">
+        <v>240</v>
+      </c>
+      <c r="J45" t="s">
         <v>198</v>
       </c>
-      <c r="I18" t="s">
-        <v>228</v>
-      </c>
-      <c r="J18" t="s">
-        <v>279</v>
-      </c>
-      <c r="K18" t="s">
-        <v>213</v>
-      </c>
-      <c r="L18" t="s">
-        <v>198</v>
-      </c>
-      <c r="M18" t="s">
+      <c r="K45" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H19">
-        <v>199</v>
-      </c>
-      <c r="I19" t="s">
-        <v>228</v>
-      </c>
-      <c r="J19" t="s">
-        <v>280</v>
-      </c>
-      <c r="K19" t="s">
-        <v>213</v>
-      </c>
-      <c r="L19" t="s">
-        <v>197</v>
-      </c>
-      <c r="M19" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H20">
-        <v>200</v>
-      </c>
-      <c r="I20" t="s">
-        <v>229</v>
-      </c>
-      <c r="J20" t="s">
-        <v>278</v>
-      </c>
-      <c r="K20" t="s">
-        <v>214</v>
-      </c>
-      <c r="L20" t="s">
-        <v>199</v>
-      </c>
-      <c r="M20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H21">
-        <v>201</v>
-      </c>
-      <c r="I21" t="s">
-        <v>229</v>
-      </c>
-      <c r="J21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K21" t="s">
-        <v>214</v>
-      </c>
-      <c r="L21" t="s">
-        <v>203</v>
-      </c>
-      <c r="M21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H22">
-        <v>202</v>
-      </c>
-      <c r="I22" t="s">
-        <v>229</v>
-      </c>
-      <c r="J22" t="s">
-        <v>280</v>
-      </c>
-      <c r="K22" t="s">
-        <v>214</v>
-      </c>
-      <c r="L22" t="s">
-        <v>132</v>
-      </c>
-      <c r="M22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H23">
-        <v>203</v>
-      </c>
-      <c r="I23" t="s">
-        <v>230</v>
-      </c>
-      <c r="J23" t="s">
-        <v>278</v>
-      </c>
-      <c r="K23" t="s">
-        <v>213</v>
-      </c>
-      <c r="L23" t="s">
-        <v>199</v>
-      </c>
-      <c r="M23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H24">
-        <v>204</v>
-      </c>
-      <c r="I24" t="s">
-        <v>230</v>
-      </c>
-      <c r="J24" t="s">
-        <v>279</v>
-      </c>
-      <c r="K24" t="s">
-        <v>213</v>
-      </c>
-      <c r="L24" t="s">
-        <v>198</v>
-      </c>
-      <c r="M24" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H25">
-        <v>205</v>
-      </c>
-      <c r="I25" t="s">
-        <v>230</v>
-      </c>
-      <c r="J25" t="s">
-        <v>281</v>
-      </c>
-      <c r="K25" t="s">
-        <v>213</v>
-      </c>
-      <c r="L25" t="s">
-        <v>205</v>
-      </c>
-      <c r="M25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H26">
-        <v>206</v>
-      </c>
-      <c r="I26" t="s">
-        <v>231</v>
-      </c>
-      <c r="J26" t="s">
-        <v>278</v>
-      </c>
-      <c r="K26" t="s">
-        <v>214</v>
-      </c>
-      <c r="L26" t="s">
-        <v>197</v>
-      </c>
-      <c r="M26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H27">
-        <v>207</v>
-      </c>
-      <c r="I27" t="s">
-        <v>231</v>
-      </c>
-      <c r="J27" t="s">
-        <v>279</v>
-      </c>
-      <c r="K27" t="s">
-        <v>213</v>
-      </c>
-      <c r="L27" t="s">
-        <v>203</v>
-      </c>
-      <c r="M27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H28">
-        <v>208</v>
-      </c>
-      <c r="I28" t="s">
-        <v>231</v>
-      </c>
-      <c r="J28" t="s">
-        <v>281</v>
-      </c>
-      <c r="K28" t="s">
-        <v>213</v>
-      </c>
-      <c r="L28" t="s">
-        <v>203</v>
-      </c>
-      <c r="M28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H29">
-        <v>209</v>
-      </c>
-      <c r="I29" t="s">
-        <v>232</v>
-      </c>
-      <c r="J29" t="s">
-        <v>278</v>
-      </c>
-      <c r="K29" t="s">
-        <v>213</v>
-      </c>
-      <c r="L29" t="s">
-        <v>132</v>
-      </c>
-      <c r="M29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H30">
-        <v>210</v>
-      </c>
-      <c r="I30" t="s">
-        <v>232</v>
-      </c>
-      <c r="J30" t="s">
-        <v>279</v>
-      </c>
-      <c r="K30" t="s">
-        <v>213</v>
-      </c>
-      <c r="L30" t="s">
-        <v>205</v>
-      </c>
-      <c r="M30" t="s">
-        <v>92</v>
+      <c r="W45" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 1, 472)</v>
+      </c>
+      <c r="X45" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 2, 472)</v>
+      </c>
+      <c r="Y45" t="str">
+        <f t="shared" si="18"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 7, 472)</v>
+      </c>
+      <c r="Z45" t="str">
+        <f t="shared" si="19"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 9, 472)</v>
+      </c>
+      <c r="AA45" t="str">
+        <f t="shared" si="20"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 14, 472)</v>
+      </c>
+      <c r="AB45" t="str">
+        <f t="shared" si="21"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 15, 472)</v>
+      </c>
+      <c r="AC45" t="str">
+        <f t="shared" si="22"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 18, 472)</v>
+      </c>
+      <c r="AD45" t="str">
+        <f t="shared" si="23"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 23, 472)</v>
       </c>
     </row>
   </sheetData>
@@ -37296,51 +39021,81 @@
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B3:B10"/>
   </mergeCells>
+  <conditionalFormatting sqref="I3:I30">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="LAB">
+      <formula>NOT(ISERROR(SEARCH("LAB",I3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="LEC">
+      <formula>NOT(ISERROR(SEARCH("LEC",I3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA2A9A05-1D5F-45E2-A0C0-AD53C78DCC2A}">
-  <dimension ref="B2:M31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF93F84-82A4-45F7-9123-90D28BA515A7}">
+  <dimension ref="B2:Z46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.6640625" customWidth="1"/>
+    <col min="13" max="18" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C2" s="25" t="s">
         <v>277</v>
       </c>
       <c r="D2" s="25"/>
+      <c r="F2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" t="s">
+        <v>223</v>
+      </c>
       <c r="H2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="I2" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="J2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K2" t="s">
-        <v>284</v>
-      </c>
-      <c r="L2" t="s">
-        <v>285</v>
-      </c>
-      <c r="M2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M2" s="2">
+        <v>3</v>
+      </c>
+      <c r="N2" s="2">
+        <v>10</v>
+      </c>
+      <c r="O2" s="2">
+        <v>12</v>
+      </c>
+      <c r="P2" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" s="26">
         <v>6</v>
       </c>
@@ -37350,26 +39105,56 @@
       <c r="D3" t="s">
         <v>271</v>
       </c>
-      <c r="H3">
+      <c r="F3">
         <v>413</v>
       </c>
+      <c r="G3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H3" t="s">
+        <v>278</v>
+      </c>
       <c r="I3" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="J3" t="s">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="K3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="P3" t="s">
+        <v>288</v>
+      </c>
+      <c r="R3" t="s">
+        <v>288</v>
+      </c>
+      <c r="U3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M3=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 413)</v>
+      </c>
+      <c r="V3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N3=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 413)</v>
+      </c>
+      <c r="W3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O3=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 413)</v>
+      </c>
+      <c r="X3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P3=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 19, 413)</v>
+      </c>
+      <c r="Y3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q3=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 413)</v>
+      </c>
+      <c r="Z3" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R3=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F3&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 413)</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B4" s="26"/>
       <c r="C4">
         <v>10</v>
@@ -37377,26 +39162,50 @@
       <c r="D4" t="s">
         <v>272</v>
       </c>
-      <c r="H4">
+      <c r="F4">
         <v>414</v>
       </c>
+      <c r="G4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" t="s">
+        <v>279</v>
+      </c>
       <c r="I4" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J4" t="s">
-        <v>279</v>
+        <v>197</v>
       </c>
       <c r="K4" t="s">
-        <v>213</v>
-      </c>
-      <c r="L4" t="s">
-        <v>197</v>
-      </c>
-      <c r="M4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="U4" t="str">
+        <f t="shared" ref="U4:U26" si="0">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M4=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 414)</v>
+      </c>
+      <c r="V4" t="str">
+        <f t="shared" ref="V4:V26" si="1">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N4=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 414)</v>
+      </c>
+      <c r="W4" t="str">
+        <f t="shared" ref="W4:W26" si="2">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O4=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 414)</v>
+      </c>
+      <c r="X4" t="str">
+        <f t="shared" ref="X4:X26" si="3">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P4=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 414)</v>
+      </c>
+      <c r="Y4" t="str">
+        <f t="shared" ref="Y4:Y26" si="4">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q4=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 414)</v>
+      </c>
+      <c r="Z4" t="str">
+        <f t="shared" ref="Z4:Z26" si="5">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R4=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F4&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 414)</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B5" s="26"/>
       <c r="C5">
         <v>12</v>
@@ -37404,26 +39213,50 @@
       <c r="D5" t="s">
         <v>273</v>
       </c>
-      <c r="H5">
+      <c r="F5">
         <v>415</v>
       </c>
+      <c r="G5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" t="s">
+        <v>280</v>
+      </c>
       <c r="I5" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="J5" t="s">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="K5" t="s">
-        <v>213</v>
-      </c>
-      <c r="L5" t="s">
-        <v>198</v>
-      </c>
-      <c r="M5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="U5" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 415)</v>
+      </c>
+      <c r="V5" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 415)</v>
+      </c>
+      <c r="W5" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 415)</v>
+      </c>
+      <c r="X5" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 415)</v>
+      </c>
+      <c r="Y5" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 415)</v>
+      </c>
+      <c r="Z5" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 415)</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B6" s="26"/>
       <c r="C6">
         <v>19</v>
@@ -37431,26 +39264,56 @@
       <c r="D6" t="s">
         <v>274</v>
       </c>
-      <c r="H6">
+      <c r="F6">
         <v>416</v>
       </c>
+      <c r="G6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" t="s">
+        <v>279</v>
+      </c>
       <c r="I6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J6" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="K6" t="s">
-        <v>214</v>
-      </c>
-      <c r="L6" t="s">
-        <v>196</v>
-      </c>
-      <c r="M6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N6" t="s">
+        <v>288</v>
+      </c>
+      <c r="R6" t="s">
+        <v>288</v>
+      </c>
+      <c r="U6" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 416)</v>
+      </c>
+      <c r="V6" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 416)</v>
+      </c>
+      <c r="W6" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 416)</v>
+      </c>
+      <c r="X6" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 416)</v>
+      </c>
+      <c r="Y6" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 416)</v>
+      </c>
+      <c r="Z6" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 416)</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7" s="26"/>
       <c r="C7">
         <v>20</v>
@@ -37458,26 +39321,53 @@
       <c r="D7" t="s">
         <v>275</v>
       </c>
-      <c r="H7">
+      <c r="F7">
         <v>417</v>
       </c>
+      <c r="G7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H7" t="s">
+        <v>280</v>
+      </c>
       <c r="I7" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="J7" t="s">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="K7" t="s">
-        <v>213</v>
-      </c>
-      <c r="L7" t="s">
-        <v>196</v>
-      </c>
-      <c r="M7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N7" t="s">
+        <v>288</v>
+      </c>
+      <c r="U7" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 417)</v>
+      </c>
+      <c r="V7" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 417)</v>
+      </c>
+      <c r="W7" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 417)</v>
+      </c>
+      <c r="X7" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 417)</v>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 417)</v>
+      </c>
+      <c r="Z7" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 417)</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" s="26"/>
       <c r="C8">
         <v>22</v>
@@ -37485,483 +39375,1669 @@
       <c r="D8" t="s">
         <v>276</v>
       </c>
-      <c r="H8">
+      <c r="F8">
         <v>418</v>
       </c>
+      <c r="G8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H8" t="s">
+        <v>282</v>
+      </c>
       <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" t="s">
+        <v>196</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" t="s">
+        <v>288</v>
+      </c>
+      <c r="U8" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 418)</v>
+      </c>
+      <c r="V8" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 418)</v>
+      </c>
+      <c r="W8" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 418)</v>
+      </c>
+      <c r="X8" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 418)</v>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 418)</v>
+      </c>
+      <c r="Z8" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 418)</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B9" s="27"/>
+      <c r="F9">
+        <v>419</v>
+      </c>
+      <c r="G9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U9" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 419)</v>
+      </c>
+      <c r="V9" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 419)</v>
+      </c>
+      <c r="W9" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 419)</v>
+      </c>
+      <c r="X9" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 419)</v>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 419)</v>
+      </c>
+      <c r="Z9" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 419)</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B10" s="27"/>
+      <c r="F10">
+        <v>420</v>
+      </c>
+      <c r="G10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H10" t="s">
+        <v>279</v>
+      </c>
+      <c r="I10" t="s">
+        <v>214</v>
+      </c>
+      <c r="J10" t="s">
+        <v>204</v>
+      </c>
+      <c r="K10" t="s">
+        <v>82</v>
+      </c>
+      <c r="U10" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 420)</v>
+      </c>
+      <c r="V10" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 420)</v>
+      </c>
+      <c r="W10" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 420)</v>
+      </c>
+      <c r="X10" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 420)</v>
+      </c>
+      <c r="Y10" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 420)</v>
+      </c>
+      <c r="Z10" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 420)</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>270</v>
+      </c>
+      <c r="F11">
+        <v>421</v>
+      </c>
+      <c r="G11" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" t="s">
+        <v>281</v>
+      </c>
+      <c r="I11" t="s">
+        <v>213</v>
+      </c>
+      <c r="J11" t="s">
+        <v>205</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="N11" t="s">
+        <v>288</v>
+      </c>
+      <c r="U11" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 421)</v>
+      </c>
+      <c r="V11" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 421)</v>
+      </c>
+      <c r="W11" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 421)</v>
+      </c>
+      <c r="X11" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 421)</v>
+      </c>
+      <c r="Y11" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 421)</v>
+      </c>
+      <c r="Z11" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 421)</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12">
+        <v>422</v>
+      </c>
+      <c r="G12" t="s">
+        <v>231</v>
+      </c>
+      <c r="H12" t="s">
+        <v>278</v>
+      </c>
+      <c r="I12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" t="s">
+        <v>197</v>
+      </c>
+      <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" t="s">
+        <v>288</v>
+      </c>
+      <c r="R12" t="s">
+        <v>288</v>
+      </c>
+      <c r="U12" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 3, 422)</v>
+      </c>
+      <c r="V12" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 422)</v>
+      </c>
+      <c r="W12" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 422)</v>
+      </c>
+      <c r="X12" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 422)</v>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 422)</v>
+      </c>
+      <c r="Z12" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 422)</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13">
+        <v>423</v>
+      </c>
+      <c r="G13" t="s">
+        <v>231</v>
+      </c>
+      <c r="H13" t="s">
+        <v>279</v>
+      </c>
+      <c r="I13" t="s">
+        <v>214</v>
+      </c>
+      <c r="J13" t="s">
+        <v>200</v>
+      </c>
+      <c r="K13" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" t="s">
+        <v>288</v>
+      </c>
+      <c r="R13" t="s">
+        <v>288</v>
+      </c>
+      <c r="U13" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 3, 423)</v>
+      </c>
+      <c r="V13" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 423)</v>
+      </c>
+      <c r="W13" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 423)</v>
+      </c>
+      <c r="X13" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 423)</v>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 423)</v>
+      </c>
+      <c r="Z13" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 423)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>424</v>
+      </c>
+      <c r="G14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" t="s">
+        <v>280</v>
+      </c>
+      <c r="I14" t="s">
+        <v>213</v>
+      </c>
+      <c r="J14" t="s">
+        <v>200</v>
+      </c>
+      <c r="K14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" t="s">
+        <v>288</v>
+      </c>
+      <c r="R14" t="s">
+        <v>288</v>
+      </c>
+      <c r="U14" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 3, 424)</v>
+      </c>
+      <c r="V14" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 424)</v>
+      </c>
+      <c r="W14" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 424)</v>
+      </c>
+      <c r="X14" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 424)</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 424)</v>
+      </c>
+      <c r="Z14" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 424)</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>425</v>
+      </c>
+      <c r="G15" t="s">
+        <v>232</v>
+      </c>
+      <c r="H15" t="s">
+        <v>278</v>
+      </c>
+      <c r="I15" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" t="s">
+        <v>82</v>
+      </c>
+      <c r="P15" t="s">
+        <v>288</v>
+      </c>
+      <c r="U15" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 425)</v>
+      </c>
+      <c r="V15" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 425)</v>
+      </c>
+      <c r="W15" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 425)</v>
+      </c>
+      <c r="X15" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 19, 425)</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 425)</v>
+      </c>
+      <c r="Z15" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 425)</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>426</v>
+      </c>
+      <c r="G16" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" t="s">
+        <v>279</v>
+      </c>
+      <c r="I16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J16" t="s">
+        <v>198</v>
+      </c>
+      <c r="K16" t="s">
+        <v>73</v>
+      </c>
+      <c r="P16" t="s">
+        <v>288</v>
+      </c>
+      <c r="U16" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 426)</v>
+      </c>
+      <c r="V16" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 426)</v>
+      </c>
+      <c r="W16" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 426)</v>
+      </c>
+      <c r="X16" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 19, 426)</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 426)</v>
+      </c>
+      <c r="Z16" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 426)</v>
+      </c>
+    </row>
+    <row r="17" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>427</v>
+      </c>
+      <c r="G17" t="s">
+        <v>232</v>
+      </c>
+      <c r="H17" t="s">
+        <v>281</v>
+      </c>
+      <c r="I17" t="s">
+        <v>213</v>
+      </c>
+      <c r="J17" t="s">
+        <v>205</v>
+      </c>
+      <c r="K17" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17" t="s">
+        <v>288</v>
+      </c>
+      <c r="P17" t="s">
+        <v>288</v>
+      </c>
+      <c r="U17" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 427)</v>
+      </c>
+      <c r="V17" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 427)</v>
+      </c>
+      <c r="W17" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 427)</v>
+      </c>
+      <c r="X17" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 19, 427)</v>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 427)</v>
+      </c>
+      <c r="Z17" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 427)</v>
+      </c>
+    </row>
+    <row r="18" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>428</v>
+      </c>
+      <c r="G18" t="s">
+        <v>228</v>
+      </c>
+      <c r="H18" t="s">
+        <v>278</v>
+      </c>
+      <c r="I18" t="s">
+        <v>214</v>
+      </c>
+      <c r="J18" t="s">
+        <v>198</v>
+      </c>
+      <c r="K18" t="s">
+        <v>73</v>
+      </c>
+      <c r="R18" t="s">
+        <v>288</v>
+      </c>
+      <c r="U18" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 428)</v>
+      </c>
+      <c r="V18" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 428)</v>
+      </c>
+      <c r="W18" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 428)</v>
+      </c>
+      <c r="X18" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 428)</v>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 428)</v>
+      </c>
+      <c r="Z18" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 428)</v>
+      </c>
+    </row>
+    <row r="19" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>429</v>
+      </c>
+      <c r="G19" t="s">
+        <v>228</v>
+      </c>
+      <c r="H19" t="s">
+        <v>279</v>
+      </c>
+      <c r="I19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" t="s">
+        <v>197</v>
+      </c>
+      <c r="K19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U19" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 429)</v>
+      </c>
+      <c r="V19" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 429)</v>
+      </c>
+      <c r="W19" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 429)</v>
+      </c>
+      <c r="X19" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 429)</v>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 429)</v>
+      </c>
+      <c r="Z19" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 429)</v>
+      </c>
+    </row>
+    <row r="20" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>430</v>
+      </c>
+      <c r="G20" t="s">
+        <v>228</v>
+      </c>
+      <c r="H20" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20" t="s">
+        <v>198</v>
+      </c>
+      <c r="K20" t="s">
+        <v>73</v>
+      </c>
+      <c r="U20" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 430)</v>
+      </c>
+      <c r="V20" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 430)</v>
+      </c>
+      <c r="W20" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 430)</v>
+      </c>
+      <c r="X20" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 430)</v>
+      </c>
+      <c r="Y20" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 430)</v>
+      </c>
+      <c r="Z20" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 430)</v>
+      </c>
+    </row>
+    <row r="21" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F21">
+        <v>431</v>
+      </c>
+      <c r="G21" t="s">
         <v>229</v>
       </c>
-      <c r="J8" t="s">
+      <c r="H21" t="s">
+        <v>279</v>
+      </c>
+      <c r="I21" t="s">
+        <v>214</v>
+      </c>
+      <c r="J21" t="s">
+        <v>196</v>
+      </c>
+      <c r="K21" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21" t="s">
+        <v>288</v>
+      </c>
+      <c r="U21" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 431)</v>
+      </c>
+      <c r="V21" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 431)</v>
+      </c>
+      <c r="W21" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 431)</v>
+      </c>
+      <c r="X21" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 431)</v>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 431)</v>
+      </c>
+      <c r="Z21" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 431)</v>
+      </c>
+    </row>
+    <row r="22" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F22">
+        <v>432</v>
+      </c>
+      <c r="G22" t="s">
+        <v>229</v>
+      </c>
+      <c r="H22" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" t="s">
+        <v>213</v>
+      </c>
+      <c r="J22" t="s">
+        <v>196</v>
+      </c>
+      <c r="K22" t="s">
+        <v>76</v>
+      </c>
+      <c r="U22" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 432)</v>
+      </c>
+      <c r="V22" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 432)</v>
+      </c>
+      <c r="W22" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 432)</v>
+      </c>
+      <c r="X22" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 432)</v>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 432)</v>
+      </c>
+      <c r="Z22" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 432)</v>
+      </c>
+    </row>
+    <row r="23" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>433</v>
+      </c>
+      <c r="G23" t="s">
+        <v>230</v>
+      </c>
+      <c r="H23" t="s">
+        <v>278</v>
+      </c>
+      <c r="I23" t="s">
+        <v>213</v>
+      </c>
+      <c r="J23" t="s">
+        <v>196</v>
+      </c>
+      <c r="K23" t="s">
+        <v>76</v>
+      </c>
+      <c r="U23" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 433)</v>
+      </c>
+      <c r="V23" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 433)</v>
+      </c>
+      <c r="W23" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 433)</v>
+      </c>
+      <c r="X23" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 433)</v>
+      </c>
+      <c r="Y23" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 433)</v>
+      </c>
+      <c r="Z23" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 433)</v>
+      </c>
+    </row>
+    <row r="24" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F24">
+        <v>434</v>
+      </c>
+      <c r="G24" t="s">
+        <v>230</v>
+      </c>
+      <c r="H24" t="s">
+        <v>279</v>
+      </c>
+      <c r="I24" t="s">
+        <v>214</v>
+      </c>
+      <c r="J24" t="s">
+        <v>204</v>
+      </c>
+      <c r="K24" t="s">
+        <v>82</v>
+      </c>
+      <c r="U24" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 434)</v>
+      </c>
+      <c r="V24" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 434)</v>
+      </c>
+      <c r="W24" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 434)</v>
+      </c>
+      <c r="X24" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 434)</v>
+      </c>
+      <c r="Y24" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 434)</v>
+      </c>
+      <c r="Z24" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 434)</v>
+      </c>
+    </row>
+    <row r="25" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F25">
+        <v>435</v>
+      </c>
+      <c r="G25" t="s">
+        <v>230</v>
+      </c>
+      <c r="H25" t="s">
+        <v>281</v>
+      </c>
+      <c r="I25" t="s">
+        <v>213</v>
+      </c>
+      <c r="J25" t="s">
+        <v>205</v>
+      </c>
+      <c r="K25" t="s">
+        <v>74</v>
+      </c>
+      <c r="N25" t="s">
+        <v>288</v>
+      </c>
+      <c r="U25" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 435)</v>
+      </c>
+      <c r="V25" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 435)</v>
+      </c>
+      <c r="W25" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 435)</v>
+      </c>
+      <c r="X25" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 435)</v>
+      </c>
+      <c r="Y25" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 435)</v>
+      </c>
+      <c r="Z25" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 435)</v>
+      </c>
+    </row>
+    <row r="26" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F26">
+        <v>436</v>
+      </c>
+      <c r="G26" t="s">
+        <v>231</v>
+      </c>
+      <c r="H26" t="s">
+        <v>278</v>
+      </c>
+      <c r="I26" t="s">
+        <v>214</v>
+      </c>
+      <c r="J26" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" t="s">
+        <v>88</v>
+      </c>
+      <c r="R26" t="s">
+        <v>288</v>
+      </c>
+      <c r="U26" t="str">
+        <f t="shared" si="0"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 436)</v>
+      </c>
+      <c r="V26" t="str">
+        <f t="shared" si="1"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 436)</v>
+      </c>
+      <c r="W26" t="str">
+        <f t="shared" si="2"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 436)</v>
+      </c>
+      <c r="X26" t="str">
+        <f t="shared" si="3"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 436)</v>
+      </c>
+      <c r="Y26" t="str">
+        <f t="shared" si="4"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 436)</v>
+      </c>
+      <c r="Z26" t="str">
+        <f t="shared" si="5"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 22, 436)</v>
+      </c>
+    </row>
+    <row r="27" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>437</v>
+      </c>
+      <c r="G27" t="s">
+        <v>231</v>
+      </c>
+      <c r="H27" t="s">
+        <v>279</v>
+      </c>
+      <c r="I27" t="s">
+        <v>214</v>
+      </c>
+      <c r="J27" t="s">
+        <v>200</v>
+      </c>
+      <c r="K27" t="s">
+        <v>78</v>
+      </c>
+      <c r="U27" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M27=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F27&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 437)</v>
+      </c>
+      <c r="V27" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N27=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F27&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 437)</v>
+      </c>
+      <c r="W27" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O27=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F27&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 437)</v>
+      </c>
+      <c r="X27" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P27=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F27&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 437)</v>
+      </c>
+      <c r="Y27" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q27=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F27&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 437)</v>
+      </c>
+      <c r="Z27" t="str">
+        <f>", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R27=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F27&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 437)</v>
+      </c>
+    </row>
+    <row r="28" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F28">
+        <v>438</v>
+      </c>
+      <c r="G28" t="s">
+        <v>231</v>
+      </c>
+      <c r="H28" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" t="s">
+        <v>200</v>
+      </c>
+      <c r="K28" t="s">
+        <v>78</v>
+      </c>
+      <c r="U28" t="str">
+        <f t="shared" ref="U28:U31" si="6">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M28=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F28&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 438)</v>
+      </c>
+      <c r="V28" t="str">
+        <f t="shared" ref="V28:V31" si="7">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N28=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F28&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 438)</v>
+      </c>
+      <c r="W28" t="str">
+        <f t="shared" ref="W28:W31" si="8">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O28=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F28&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 438)</v>
+      </c>
+      <c r="X28" t="str">
+        <f t="shared" ref="X28:X31" si="9">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P28=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F28&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 438)</v>
+      </c>
+      <c r="Y28" t="str">
+        <f t="shared" ref="Y28:Y31" si="10">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q28=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F28&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 438)</v>
+      </c>
+      <c r="Z28" t="str">
+        <f t="shared" ref="Z28:Z31" si="11">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R28=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F28&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 438)</v>
+      </c>
+    </row>
+    <row r="29" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <v>439</v>
+      </c>
+      <c r="G29" t="s">
+        <v>232</v>
+      </c>
+      <c r="H29" t="s">
+        <v>278</v>
+      </c>
+      <c r="I29" t="s">
+        <v>213</v>
+      </c>
+      <c r="J29" t="s">
+        <v>204</v>
+      </c>
+      <c r="K29" t="s">
+        <v>82</v>
+      </c>
+      <c r="U29" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 439)</v>
+      </c>
+      <c r="V29" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 439)</v>
+      </c>
+      <c r="W29" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 439)</v>
+      </c>
+      <c r="X29" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 439)</v>
+      </c>
+      <c r="Y29" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 439)</v>
+      </c>
+      <c r="Z29" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 439)</v>
+      </c>
+    </row>
+    <row r="30" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>440</v>
+      </c>
+      <c r="G30" t="s">
+        <v>232</v>
+      </c>
+      <c r="H30" t="s">
+        <v>279</v>
+      </c>
+      <c r="I30" t="s">
+        <v>213</v>
+      </c>
+      <c r="J30" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" t="s">
+        <v>73</v>
+      </c>
+      <c r="U30" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 440)</v>
+      </c>
+      <c r="V30" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 440)</v>
+      </c>
+      <c r="W30" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 440)</v>
+      </c>
+      <c r="X30" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 440)</v>
+      </c>
+      <c r="Y30" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 440)</v>
+      </c>
+      <c r="Z30" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 440)</v>
+      </c>
+    </row>
+    <row r="31" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <v>441</v>
+      </c>
+      <c r="G31" t="s">
+        <v>232</v>
+      </c>
+      <c r="H31" t="s">
+        <v>280</v>
+      </c>
+      <c r="I31" t="s">
+        <v>213</v>
+      </c>
+      <c r="J31" t="s">
+        <v>205</v>
+      </c>
+      <c r="K31" t="s">
+        <v>92</v>
+      </c>
+      <c r="N31" t="s">
+        <v>288</v>
+      </c>
+      <c r="U31" t="str">
+        <f t="shared" si="6"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 441)</v>
+      </c>
+      <c r="V31" t="str">
+        <f t="shared" si="7"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), false, 10, 441)</v>
+      </c>
+      <c r="W31" t="str">
+        <f t="shared" si="8"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 441)</v>
+      </c>
+      <c r="X31" t="str">
+        <f t="shared" si="9"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 441)</v>
+      </c>
+      <c r="Y31" t="str">
+        <f t="shared" si="10"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 441)</v>
+      </c>
+      <c r="Z31" t="str">
+        <f t="shared" si="11"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 441)</v>
+      </c>
+    </row>
+    <row r="34" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="M34">
+        <v>3</v>
+      </c>
+      <c r="N34">
+        <v>10</v>
+      </c>
+      <c r="O34">
+        <v>12</v>
+      </c>
+      <c r="P34">
+        <v>19</v>
+      </c>
+      <c r="Q34">
+        <v>20</v>
+      </c>
+      <c r="R34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F35">
+        <v>480</v>
+      </c>
+      <c r="G35" t="s">
+        <v>229</v>
+      </c>
+      <c r="H35" t="s">
+        <v>281</v>
+      </c>
+      <c r="I35" t="s">
+        <v>239</v>
+      </c>
+      <c r="J35" t="s">
+        <v>197</v>
+      </c>
+      <c r="K35" t="s">
+        <v>84</v>
+      </c>
+      <c r="U35" t="str">
+        <f t="shared" ref="U32:U46" si="12">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(M35=$D$13,$D$13,$D$12)&amp;", "&amp;M$2&amp;", "&amp;$F35&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 480)</v>
+      </c>
+      <c r="V35" t="str">
+        <f t="shared" ref="V32:V46" si="13">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(N35=$D$13,$D$13,$D$12)&amp;", "&amp;N$2&amp;", "&amp;$F35&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 480)</v>
+      </c>
+      <c r="W35" t="str">
+        <f t="shared" ref="W32:W46" si="14">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(O35=$D$13,$D$13,$D$12)&amp;", "&amp;O$2&amp;", "&amp;$F35&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 480)</v>
+      </c>
+      <c r="X35" t="str">
+        <f t="shared" ref="X32:X46" si="15">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(P35=$D$13,$D$13,$D$12)&amp;", "&amp;P$2&amp;", "&amp;$F35&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 480)</v>
+      </c>
+      <c r="Y35" t="str">
+        <f t="shared" ref="Y32:Y46" si="16">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(Q35=$D$13,$D$13,$D$12)&amp;", "&amp;Q$2&amp;", "&amp;$F35&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 480)</v>
+      </c>
+      <c r="Z35" t="str">
+        <f t="shared" ref="Z32:Z46" si="17">", (nextval('students_attendance_attendance_id_seq'), "&amp;IF(R35=$D$13,$D$13,$D$12)&amp;", "&amp;R$2&amp;", "&amp;$F35&amp;")"</f>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 480)</v>
+      </c>
+    </row>
+    <row r="36" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F36">
+        <v>467</v>
+      </c>
+      <c r="G36" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" t="s">
         <v>282</v>
       </c>
-      <c r="K8" t="s">
-        <v>215</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="I36" t="s">
+        <v>239</v>
+      </c>
+      <c r="J36" t="s">
+        <v>205</v>
+      </c>
+      <c r="K36" t="s">
+        <v>74</v>
+      </c>
+      <c r="U36" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 467)</v>
+      </c>
+      <c r="V36" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 467)</v>
+      </c>
+      <c r="W36" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 467)</v>
+      </c>
+      <c r="X36" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 467)</v>
+      </c>
+      <c r="Y36" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 467)</v>
+      </c>
+      <c r="Z36" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 467)</v>
+      </c>
+    </row>
+    <row r="37" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F37">
+        <v>468</v>
+      </c>
+      <c r="G37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" t="s">
+        <v>279</v>
+      </c>
+      <c r="I37" t="s">
+        <v>239</v>
+      </c>
+      <c r="J37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K37" t="s">
+        <v>84</v>
+      </c>
+      <c r="U37" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 468)</v>
+      </c>
+      <c r="V37" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 468)</v>
+      </c>
+      <c r="W37" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 468)</v>
+      </c>
+      <c r="X37" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 468)</v>
+      </c>
+      <c r="Y37" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 468)</v>
+      </c>
+      <c r="Z37" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 468)</v>
+      </c>
+    </row>
+    <row r="38" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F38">
+        <v>479</v>
+      </c>
+      <c r="G38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" t="s">
+        <v>289</v>
+      </c>
+      <c r="I38" t="s">
+        <v>239</v>
+      </c>
+      <c r="J38" t="s">
+        <v>205</v>
+      </c>
+      <c r="K38" t="s">
+        <v>74</v>
+      </c>
+      <c r="U38" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 479)</v>
+      </c>
+      <c r="V38" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 479)</v>
+      </c>
+      <c r="W38" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 479)</v>
+      </c>
+      <c r="X38" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 479)</v>
+      </c>
+      <c r="Y38" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 479)</v>
+      </c>
+      <c r="Z38" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 479)</v>
+      </c>
+    </row>
+    <row r="39" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F39">
+        <v>477</v>
+      </c>
+      <c r="G39" t="s">
+        <v>232</v>
+      </c>
+      <c r="H39" t="s">
+        <v>281</v>
+      </c>
+      <c r="I39" t="s">
+        <v>239</v>
+      </c>
+      <c r="J39" t="s">
+        <v>200</v>
+      </c>
+      <c r="K39" t="s">
+        <v>78</v>
+      </c>
+      <c r="U39" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 477)</v>
+      </c>
+      <c r="V39" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 477)</v>
+      </c>
+      <c r="W39" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 477)</v>
+      </c>
+      <c r="X39" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 477)</v>
+      </c>
+      <c r="Y39" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 477)</v>
+      </c>
+      <c r="Z39" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 477)</v>
+      </c>
+    </row>
+    <row r="40" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F40">
+        <v>465</v>
+      </c>
+      <c r="G40" t="s">
+        <v>232</v>
+      </c>
+      <c r="H40" t="s">
+        <v>279</v>
+      </c>
+      <c r="I40" t="s">
+        <v>239</v>
+      </c>
+      <c r="J40" t="s">
+        <v>200</v>
+      </c>
+      <c r="K40" t="s">
+        <v>78</v>
+      </c>
+      <c r="U40" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 465)</v>
+      </c>
+      <c r="V40" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 465)</v>
+      </c>
+      <c r="W40" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 465)</v>
+      </c>
+      <c r="X40" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 465)</v>
+      </c>
+      <c r="Y40" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 465)</v>
+      </c>
+      <c r="Z40" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 465)</v>
+      </c>
+    </row>
+    <row r="41" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F41">
+        <v>478</v>
+      </c>
+      <c r="G41" t="s">
+        <v>228</v>
+      </c>
+      <c r="H41" t="s">
+        <v>281</v>
+      </c>
+      <c r="I41" t="s">
+        <v>240</v>
+      </c>
+      <c r="J41" t="s">
+        <v>204</v>
+      </c>
+      <c r="K41" t="s">
+        <v>82</v>
+      </c>
+      <c r="U41" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 478)</v>
+      </c>
+      <c r="V41" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 478)</v>
+      </c>
+      <c r="W41" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 478)</v>
+      </c>
+      <c r="X41" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 478)</v>
+      </c>
+      <c r="Y41" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 478)</v>
+      </c>
+      <c r="Z41" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 478)</v>
+      </c>
+    </row>
+    <row r="42" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F42">
+        <v>466</v>
+      </c>
+      <c r="G42" t="s">
+        <v>228</v>
+      </c>
+      <c r="H42" t="s">
+        <v>279</v>
+      </c>
+      <c r="I42" t="s">
+        <v>240</v>
+      </c>
+      <c r="J42" t="s">
+        <v>204</v>
+      </c>
+      <c r="K42" t="s">
+        <v>82</v>
+      </c>
+      <c r="U42" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 466)</v>
+      </c>
+      <c r="V42" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 466)</v>
+      </c>
+      <c r="W42" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 466)</v>
+      </c>
+      <c r="X42" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 466)</v>
+      </c>
+      <c r="Y42" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 466)</v>
+      </c>
+      <c r="Z42" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 466)</v>
+      </c>
+    </row>
+    <row r="43" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F43">
+        <v>464</v>
+      </c>
+      <c r="G43" t="s">
+        <v>231</v>
+      </c>
+      <c r="H43" t="s">
+        <v>279</v>
+      </c>
+      <c r="I43" t="s">
+        <v>240</v>
+      </c>
+      <c r="J43" t="s">
+        <v>198</v>
+      </c>
+      <c r="K43" t="s">
+        <v>73</v>
+      </c>
+      <c r="U43" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 464)</v>
+      </c>
+      <c r="V43" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 464)</v>
+      </c>
+      <c r="W43" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 464)</v>
+      </c>
+      <c r="X43" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 464)</v>
+      </c>
+      <c r="Y43" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 464)</v>
+      </c>
+      <c r="Z43" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 464)</v>
+      </c>
+    </row>
+    <row r="44" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <v>476</v>
+      </c>
+      <c r="G44" t="s">
+        <v>231</v>
+      </c>
+      <c r="H44" t="s">
+        <v>281</v>
+      </c>
+      <c r="I44" t="s">
+        <v>240</v>
+      </c>
+      <c r="J44" t="s">
+        <v>198</v>
+      </c>
+      <c r="K44" t="s">
+        <v>73</v>
+      </c>
+      <c r="U44" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 476)</v>
+      </c>
+      <c r="V44" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 476)</v>
+      </c>
+      <c r="W44" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 476)</v>
+      </c>
+      <c r="X44" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 476)</v>
+      </c>
+      <c r="Y44" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 476)</v>
+      </c>
+      <c r="Z44" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 476)</v>
+      </c>
+    </row>
+    <row r="45" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <v>475</v>
+      </c>
+      <c r="G45" t="s">
+        <v>243</v>
+      </c>
+      <c r="H45" t="s">
+        <v>281</v>
+      </c>
+      <c r="I45" t="s">
+        <v>240</v>
+      </c>
+      <c r="J45" t="s">
         <v>196</v>
       </c>
-      <c r="M8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H9">
-        <v>419</v>
-      </c>
-      <c r="I9" t="s">
-        <v>230</v>
-      </c>
-      <c r="J9" t="s">
-        <v>278</v>
-      </c>
-      <c r="K9" t="s">
-        <v>213</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="K45" t="s">
+        <v>76</v>
+      </c>
+      <c r="U45" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 475)</v>
+      </c>
+      <c r="V45" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 475)</v>
+      </c>
+      <c r="W45" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 475)</v>
+      </c>
+      <c r="X45" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 475)</v>
+      </c>
+      <c r="Y45" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 475)</v>
+      </c>
+      <c r="Z45" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 475)</v>
+      </c>
+    </row>
+    <row r="46" spans="6:26" x14ac:dyDescent="0.3">
+      <c r="F46">
+        <v>463</v>
+      </c>
+      <c r="G46" t="s">
+        <v>243</v>
+      </c>
+      <c r="H46" t="s">
+        <v>279</v>
+      </c>
+      <c r="I46" t="s">
+        <v>240</v>
+      </c>
+      <c r="J46" t="s">
         <v>196</v>
       </c>
-      <c r="M9" t="s">
+      <c r="K46" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H10">
-        <v>420</v>
-      </c>
-      <c r="I10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" t="s">
-        <v>279</v>
-      </c>
-      <c r="K10" t="s">
-        <v>214</v>
-      </c>
-      <c r="L10" t="s">
-        <v>204</v>
-      </c>
-      <c r="M10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H11">
-        <v>421</v>
-      </c>
-      <c r="I11" t="s">
-        <v>230</v>
-      </c>
-      <c r="J11" t="s">
-        <v>281</v>
-      </c>
-      <c r="K11" t="s">
-        <v>213</v>
-      </c>
-      <c r="L11" t="s">
-        <v>205</v>
-      </c>
-      <c r="M11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H12">
-        <v>422</v>
-      </c>
-      <c r="I12" t="s">
-        <v>231</v>
-      </c>
-      <c r="J12" t="s">
-        <v>278</v>
-      </c>
-      <c r="K12" t="s">
-        <v>214</v>
-      </c>
-      <c r="L12" t="s">
-        <v>197</v>
-      </c>
-      <c r="M12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <v>423</v>
-      </c>
-      <c r="I13" t="s">
-        <v>231</v>
-      </c>
-      <c r="J13" t="s">
-        <v>279</v>
-      </c>
-      <c r="K13" t="s">
-        <v>214</v>
-      </c>
-      <c r="L13" t="s">
-        <v>200</v>
-      </c>
-      <c r="M13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H14">
-        <v>424</v>
-      </c>
-      <c r="I14" t="s">
-        <v>231</v>
-      </c>
-      <c r="J14" t="s">
-        <v>280</v>
-      </c>
-      <c r="K14" t="s">
-        <v>213</v>
-      </c>
-      <c r="L14" t="s">
-        <v>200</v>
-      </c>
-      <c r="M14" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H15">
-        <v>425</v>
-      </c>
-      <c r="I15" t="s">
-        <v>232</v>
-      </c>
-      <c r="J15" t="s">
-        <v>278</v>
-      </c>
-      <c r="K15" t="s">
-        <v>215</v>
-      </c>
-      <c r="L15" t="s">
-        <v>204</v>
-      </c>
-      <c r="M15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H16">
-        <v>426</v>
-      </c>
-      <c r="I16" t="s">
-        <v>232</v>
-      </c>
-      <c r="J16" t="s">
-        <v>279</v>
-      </c>
-      <c r="K16" t="s">
-        <v>213</v>
-      </c>
-      <c r="L16" t="s">
-        <v>198</v>
-      </c>
-      <c r="M16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H17">
-        <v>427</v>
-      </c>
-      <c r="I17" t="s">
-        <v>232</v>
-      </c>
-      <c r="J17" t="s">
-        <v>281</v>
-      </c>
-      <c r="K17" t="s">
-        <v>213</v>
-      </c>
-      <c r="L17" t="s">
-        <v>205</v>
-      </c>
-      <c r="M17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H18">
-        <v>428</v>
-      </c>
-      <c r="I18" t="s">
-        <v>228</v>
-      </c>
-      <c r="J18" t="s">
-        <v>278</v>
-      </c>
-      <c r="K18" t="s">
-        <v>214</v>
-      </c>
-      <c r="L18" t="s">
-        <v>198</v>
-      </c>
-      <c r="M18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H19">
-        <v>429</v>
-      </c>
-      <c r="I19" t="s">
-        <v>228</v>
-      </c>
-      <c r="J19" t="s">
-        <v>279</v>
-      </c>
-      <c r="K19" t="s">
-        <v>213</v>
-      </c>
-      <c r="L19" t="s">
-        <v>197</v>
-      </c>
-      <c r="M19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H20">
-        <v>430</v>
-      </c>
-      <c r="I20" t="s">
-        <v>228</v>
-      </c>
-      <c r="J20" t="s">
-        <v>280</v>
-      </c>
-      <c r="K20" t="s">
-        <v>213</v>
-      </c>
-      <c r="L20" t="s">
-        <v>198</v>
-      </c>
-      <c r="M20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H21">
-        <v>431</v>
-      </c>
-      <c r="I21" t="s">
-        <v>229</v>
-      </c>
-      <c r="J21" t="s">
-        <v>279</v>
-      </c>
-      <c r="K21" t="s">
-        <v>214</v>
-      </c>
-      <c r="L21" t="s">
-        <v>196</v>
-      </c>
-      <c r="M21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H22">
-        <v>432</v>
-      </c>
-      <c r="I22" t="s">
-        <v>229</v>
-      </c>
-      <c r="J22" t="s">
-        <v>280</v>
-      </c>
-      <c r="K22" t="s">
-        <v>213</v>
-      </c>
-      <c r="L22" t="s">
-        <v>196</v>
-      </c>
-      <c r="M22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H23">
-        <v>433</v>
-      </c>
-      <c r="I23" t="s">
-        <v>230</v>
-      </c>
-      <c r="J23" t="s">
-        <v>278</v>
-      </c>
-      <c r="K23" t="s">
-        <v>213</v>
-      </c>
-      <c r="L23" t="s">
-        <v>196</v>
-      </c>
-      <c r="M23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H24">
-        <v>434</v>
-      </c>
-      <c r="I24" t="s">
-        <v>230</v>
-      </c>
-      <c r="J24" t="s">
-        <v>279</v>
-      </c>
-      <c r="K24" t="s">
-        <v>214</v>
-      </c>
-      <c r="L24" t="s">
-        <v>204</v>
-      </c>
-      <c r="M24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H25">
-        <v>435</v>
-      </c>
-      <c r="I25" t="s">
-        <v>230</v>
-      </c>
-      <c r="J25" t="s">
-        <v>281</v>
-      </c>
-      <c r="K25" t="s">
-        <v>213</v>
-      </c>
-      <c r="L25" t="s">
-        <v>205</v>
-      </c>
-      <c r="M25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H26">
-        <v>436</v>
-      </c>
-      <c r="I26" t="s">
-        <v>231</v>
-      </c>
-      <c r="J26" t="s">
-        <v>278</v>
-      </c>
-      <c r="K26" t="s">
-        <v>214</v>
-      </c>
-      <c r="L26" t="s">
-        <v>197</v>
-      </c>
-      <c r="M26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H27">
-        <v>437</v>
-      </c>
-      <c r="I27" t="s">
-        <v>231</v>
-      </c>
-      <c r="J27" t="s">
-        <v>279</v>
-      </c>
-      <c r="K27" t="s">
-        <v>214</v>
-      </c>
-      <c r="L27" t="s">
-        <v>200</v>
-      </c>
-      <c r="M27" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H28">
-        <v>438</v>
-      </c>
-      <c r="I28" t="s">
-        <v>231</v>
-      </c>
-      <c r="J28" t="s">
-        <v>280</v>
-      </c>
-      <c r="K28" t="s">
-        <v>213</v>
-      </c>
-      <c r="L28" t="s">
-        <v>200</v>
-      </c>
-      <c r="M28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H29">
-        <v>439</v>
-      </c>
-      <c r="I29" t="s">
-        <v>232</v>
-      </c>
-      <c r="J29" t="s">
-        <v>278</v>
-      </c>
-      <c r="K29" t="s">
-        <v>213</v>
-      </c>
-      <c r="L29" t="s">
-        <v>204</v>
-      </c>
-      <c r="M29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H30">
-        <v>440</v>
-      </c>
-      <c r="I30" t="s">
-        <v>232</v>
-      </c>
-      <c r="J30" t="s">
-        <v>279</v>
-      </c>
-      <c r="K30" t="s">
-        <v>213</v>
-      </c>
-      <c r="L30" t="s">
-        <v>198</v>
-      </c>
-      <c r="M30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="8:13" x14ac:dyDescent="0.3">
-      <c r="H31">
-        <v>441</v>
-      </c>
-      <c r="I31" t="s">
-        <v>232</v>
-      </c>
-      <c r="J31" t="s">
-        <v>280</v>
-      </c>
-      <c r="K31" t="s">
-        <v>213</v>
-      </c>
-      <c r="L31" t="s">
-        <v>205</v>
-      </c>
-      <c r="M31" t="s">
-        <v>92</v>
+      <c r="U46" t="str">
+        <f t="shared" si="12"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 3, 463)</v>
+      </c>
+      <c r="V46" t="str">
+        <f t="shared" si="13"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 10, 463)</v>
+      </c>
+      <c r="W46" t="str">
+        <f t="shared" si="14"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 12, 463)</v>
+      </c>
+      <c r="X46" t="str">
+        <f t="shared" si="15"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 19, 463)</v>
+      </c>
+      <c r="Y46" t="str">
+        <f t="shared" si="16"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 20, 463)</v>
+      </c>
+      <c r="Z46" t="str">
+        <f t="shared" si="17"/>
+        <v>, (nextval('students_attendance_attendance_id_seq'), true, 22, 463)</v>
       </c>
     </row>
   </sheetData>
@@ -37969,6 +41045,14 @@
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B3:B8"/>
   </mergeCells>
+  <conditionalFormatting sqref="I3:I30">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="LAB">
+      <formula>NOT(ISERROR(SEARCH("LAB",I3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="LEC">
+      <formula>NOT(ISERROR(SEARCH("LEC",I3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/данные/полезно.xlsx
+++ b/данные/полезно.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\irina.mashkova\Documents\GitHub\College\данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11107A87-C97E-43CC-A4DF-DFBAD8492D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AD7B28-2846-46F2-B8E2-48B766E784DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="604" firstSheet="2" activeTab="6" xr2:uid="{626BA957-AA12-44BE-A960-46A94CAF7B15}"/>
   </bookViews>
